--- a/output/pdf_financials_xlsx/KUYA.xlsx
+++ b/output/pdf_financials_xlsx/KUYA.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/KUYA.xlsx
+++ b/output/pdf_financials_xlsx/KUYA.xlsx
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.015634</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.62576</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.785353</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-2.518775</v>
+        <v>2.518775</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-4.110038</v>
+        <v>4.110038</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-0.588674</v>
+        <v>0.588674</v>
       </c>
     </row>
     <row r="11">
@@ -600,18 +600,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-4.746434</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>4.260167</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.275931</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-3.606534</v>
       </c>
     </row>
     <row r="12">
@@ -637,13 +633,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -701,13 +697,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -2659,7 +2655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4645,13 +4641,13 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>-2.518775</v>
+        <v>2.518775</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-4.110038</v>
+        <v>4.110038</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.588674</v>
+        <v>0.588674</v>
       </c>
     </row>
     <row r="65">
@@ -4916,7 +4912,11 @@
           <t>Salaries and benefits (Note 12)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -5005,7 +5005,11 @@
           <t>Transfer agent</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>0.015634</v>
       </c>
@@ -5069,13 +5073,13 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>-2.227659</v>
+        <v>2.227659</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-2.316022</v>
+        <v>2.316022</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>-2.954785</v>
+        <v>2.954785</v>
       </c>
     </row>
     <row r="79">
@@ -5094,7 +5098,11 @@
           <t>Operating loss</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E79" s="5" t="n">
         <v>-4.746434</v>
       </c>
@@ -5386,12 +5394,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>December 31, 2024 107,869,395 $ 47,698,391 $ 1,879,382 $ (2,277,223) $</t>
+          <t>Total 20,066,781 8,591,749 (167,919) (30,552) 515,592 229,134 5,483,344 - - 376,583 1,105,093</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -5401,10 +5409,10 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>20.066781</v>
+        <v>32.585432</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-27.233769</v>
+        <v>-3.584373</v>
       </c>
     </row>
     <row r="90">
@@ -5415,12 +5423,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Weighted average number of common</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Issuance of units for cash (Note 9) 29,740,000 7,688,835 902,914 -</t>
+          <t>- - - - - - 529,217 - - - Deficit (27,233,769)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -5430,12 +5438,10 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>8.591749</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-30.288925</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-3.584373</v>
       </c>
     </row>
     <row r="91">
@@ -5446,12 +5452,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>$                   $       EQUITY                        Capital</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Share issue costs (Note 9) - (201,394) 33,475 -</t>
+          <t>$                   $       EQUITY                        Capital</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -5460,8 +5466,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>-0.167919</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5477,12 +5485,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement</t>
+          <t>$                   $       EQUITY                        Capital</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of restricted share units (Notes 9 and 10) 462,500 93,116 (123,668) -</t>
+          <t>Share Number shares 462,500 904,426 of 2,580,966 consolidated 107,869,395 29,740,000</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -5492,12 +5500,10 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.030552</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>161.327628</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>19.770341</v>
       </c>
     </row>
     <row r="93">
@@ -5508,12 +5514,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Issuance of common shares on conversion</t>
+          <t>9)                                          of   of         CHANGES                                            10)                                                            and                                                                                                                                                                                                                                                          integral</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Issuance of common shares on conversion of convertible debentures (Notes 8 and 9) 2,580,966 515,592 - -</t>
+          <t>Total 24,474,634 2,785,306 (455,934) (95,745) 70,353 - 331,787 364,552 128,304 - - 299,373 (1,788,643)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -5523,12 +5529,10 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.5155920000000001</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20.066781</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-6.047206</v>
       </c>
     </row>
     <row r="94">
@@ -5539,12 +5543,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>9)                                          of   of         CHANGES                                            10)                                                            and                                                                                                                                                                                                                                                          integral</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of options (Note 9) 904,426 445,038 (215,904) -</t>
+          <t>9)                                          of   of         CHANGES                                            10)                                                            and                                                                                                                                                                                                                                                          integral total</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -5553,8 +5557,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>0.229134</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5570,12 +5576,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>9)                                          of   of         CHANGES                                            10)                                                            and                                                                                                                                                                                                                                                          integral</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of warrants (Note 9) 19,770,341 5,708,290 (224,946) -</t>
+          <t>Deficit (21,210,951)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -5585,12 +5591,10 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>5.483344</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-27.233769</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-6.047206</v>
       </c>
     </row>
     <row r="96">
@@ -5601,12 +5605,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>9)                                          of   of         CHANGES                                            10)                                                            and                                                                                                                                                                                                                                                          integral</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Options forfeited or expired (Note 10) - - (529,217) -</t>
+          <t>70,353 - - - - - statements. (cont’d…) Amount 44,177,779 2,785,306 (455,934) (95,745) 212,984 331,787 375,675</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -5615,13 +5619,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F96" s="5" t="n">
+        <v>47.698391</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.529217</v>
+        <v>0.296186</v>
       </c>
     </row>
     <row r="97">
@@ -5632,12 +5634,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>$                     $       EQUITY                        Capital</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Warrants expired (Note 9) - 242,232 (242,232) -</t>
+          <t>$                     $       EQUITY                        Capital</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -5665,12 +5667,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>$                     $       EQUITY                        Capital</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10) - - 376,583 -</t>
+          <t>Share Number shares 267,907 850,000 of 2,005,166 1,348,432 consolidated 92,922,899</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -5680,12 +5682,10 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.376583</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>107.869395</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>10.474991</v>
       </c>
     </row>
     <row r="99">
@@ -5696,12 +5696,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Foreign currency translation - - - 1,105,093</t>
+          <t>10) of CHANGES issue 9) and integral OF and 8</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -5711,12 +5711,10 @@
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>1.105093</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1e-05</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>1e-05</v>
       </c>
     </row>
     <row r="100">
@@ -5727,27 +5725,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
+          <t>Revenue total</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E100" s="5" t="n">
-        <v>-6.047206</v>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-3.584373</v>
-      </c>
-      <c r="G100" s="5" t="n">
-        <v>-3.584373</v>
+        <v>0.150129</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -5758,25 +5760,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>Property expenses</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>December 31, 2025 161,327,628 $ 62,190,100 $ 1,856,387 $ (1,172,130) $</t>
+          <t>Exploration and evaluation expenditures (Notes 5 and 11)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="5" t="n">
+        <v>2.518775</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>32.585432</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>-30.288925</v>
+        <v>4.110038</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -5787,23 +5789,25 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>December 31, 2023 92,922,899 $ 44,177,779 $ 1,996,386 $ (488,580) $</t>
+          <t>Administrative costs</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" s="5" t="n">
-        <v>24.474634</v>
+        <v>0.061496</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>24.474634</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>-21.210951</v>
+        <v>0.107372</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -5814,22 +5818,20 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Issuance of units for cash (Note 9) 10,474,991 2,785,306 - -</t>
+          <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="5" t="n">
+        <v>0.09998799999999999</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>2.785306</v>
+        <v>0.098493</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5845,22 +5847,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Flow-through share premium (Note 9) - (455,934) - -</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees (Note 11)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0.296402</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.455934</v>
+        <v>0.318867</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5876,22 +5880,20 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Share issue costs (Note 9) - (95,745) - -</t>
+          <t>Share-based compensation (Notes 9 and 11)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="5" t="n">
+        <v>0.316925</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-0.095745</v>
+        <v>0.299373</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5907,22 +5909,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Issuance of common shares for share issue</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Issuance of common shares for share issue costs (Note 9) 267,907 70,353 - -</t>
+          <t>Wages and benefits (Note 11)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="5" t="n">
+        <v>0.6866679999999999</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.070353</v>
+        <v>0.614394</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5938,24 +5938,20 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of restricted share units (Notes 9 and 10) 850,000 212,984 (212,984) -</t>
+          <t>Accretion expense (Notes 5 and 7)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="5" t="n">
+        <v>-0.059693</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>-0.108765</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5971,22 +5967,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Issuance of common shares on conversion</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Issuance of common shares on conversion of convertible debentures (Notes 8 and 9) 2,005,166 331,787 - -</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange gain (loss)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0.013207</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.331787</v>
+        <v>-0.054886</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -6002,22 +6000,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of warrants (Note 9) 1,348,432 375,675 (11,123) -</t>
+          <t>Gain on settlement of accounts payable and accrued liabilities (Note 8)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>0.364552</v>
+      <c r="E109" s="5" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -6033,22 +6031,26 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Debt unit warrants (Note 8) - - 128,304 -</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.128304</v>
+        <v>0.036003</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -6064,27 +6066,25 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Options forfeited or expired (Note 10) - - (22,817) -</t>
+          <t>Recognition of flow-through share premium (Note 8)</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>0.022817</v>
+      <c r="E111" s="5" t="n">
+        <v>0.242573</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.356373</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6095,27 +6095,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Warrants expired (Note 9) - 296,186 (297,757) -</t>
+          <t>Gain on settlement of accounts payable total</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>0.001571</v>
+      <c r="E112" s="5" t="n">
+        <v>0.209527</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.228725</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -6126,22 +6124,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10) - - 299,373 -</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>-4.536907</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.299373</v>
+        <v>-6.047206</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6157,20 +6157,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Foreign currency translation - - - (1,788,643)</t>
+          <t>December 31, 2022 58,831,801 $ 37,200,411 $ 2,212,430 $ (992,917) $</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" s="5" t="n">
-        <v>-1.788643</v>
+        <v>21.424561</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>-1.788643</v>
+        <v>-16.995363</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6186,23 +6186,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>December 31, 2024 107,869,395 $ 47,698,391 $ 1,879,382 $ (2,277,223) $</t>
+          <t>Issuance of units for cash (Note 8) 29,166,123 5,875,730 138,331 -</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" s="5" t="n">
-        <v>20.066781</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>20.066781</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>-27.233769</v>
+        <v>6.014061</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6213,26 +6217,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Revenue total</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>0.150129</v>
+          <t>Flow-through share premium (Note 8) - (175,627) - -</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>-0.175627</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6248,20 +6248,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Property expenses</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Notes 5 and 11)</t>
+          <t>Share issue costs - (299,159) 74,677 -</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" s="5" t="n">
-        <v>2.518775</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>4.110038</v>
+        <v>-0.224482</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6277,20 +6279,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>exploration and evaluation assets</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Administrative costs</t>
+          <t>(Notes 5 and 8) 4,369,370 1,057,491 - -</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" s="5" t="n">
-        <v>0.061496</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.107372</v>
+        <v>1.057491</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -6306,20 +6310,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Directors’ fees (Note 11)</t>
+          <t>Issuance of common shares on exercise of options (Notes 8 and 9) 200 250 (114) -</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" s="5" t="n">
-        <v>0.09998799999999999</v>
-      </c>
-      <c r="F119" s="5" t="n">
-        <v>0.098493</v>
+        <v>0.000136</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6335,24 +6341,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Professional fees (Note 11)</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>(Note 8) 405,405 94,139 - -</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" s="5" t="n">
-        <v>0.296402</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>0.318867</v>
+        <v>0.094139</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6368,20 +6372,24 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Issuance of common shares on settlement of</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 9 and 11)</t>
+          <t>Issuance of common shares on settlement of restricted share units (Notes 8 and 9) 150,000 65,895 (65,895) -</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" s="5" t="n">
-        <v>0.316925</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>0.299373</v>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6397,20 +6405,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Issuance of common shares on settlement of</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Wages and benefits (Note 11)</t>
+          <t>Options forfeited or expired (Note 9) - - (269,307) -</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" s="5" t="n">
-        <v>0.6866679999999999</v>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.614394</v>
+        <v>0.269307</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6426,20 +6436,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Issuance of common shares on settlement of</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Accretion expense (Notes 5 and 7)</t>
+          <t>Warrants expired (Note 8) - 358,649 (410,661) -</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
-      <c r="E123" s="5" t="n">
-        <v>-0.059693</v>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F123" s="5" t="n">
-        <v>-0.108765</v>
+        <v>0.052012</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6455,24 +6467,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Issuance of common shares on settlement of</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss)</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 9) - - 316,925 -</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
       <c r="E124" s="5" t="n">
-        <v>0.013207</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>-0.054886</v>
+        <v>0.316925</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6488,17 +6498,17 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>Issuance of common shares on settlement of</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable and accrued liabilities (Note 8)</t>
+          <t>Foreign currency translation - - - 504,337</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" s="5" t="n">
-        <v>0.01344</v>
+        <v>0.504337</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -6519,26 +6529,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>Issuance of common shares on settlement of</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Loss for the year - - - -</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="n">
+        <v>-4.536907</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.036003</v>
+        <v>-4.536907</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6554,20 +6562,20 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>Issuance of common shares on settlement of</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Recognition of flow-through share premium (Note 8)</t>
+          <t>December 31, 2023 92,922,899 $ 44,177,779 $ 1,996,386 $ (488,580) $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" s="5" t="n">
-        <v>0.242573</v>
+        <v>24.474634</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0.356373</v>
+        <v>-21.210951</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6583,20 +6591,20 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable total</t>
+          <t>December 31, 2023 92,922,899 $ 44,177,779 $ 1,996,386 $ (488,580) $</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" s="5" t="n">
-        <v>0.209527</v>
+        <v>24.474634</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.228725</v>
+        <v>-21.210951</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6612,24 +6620,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of units for cash (Note 8) 10,474,991 2,785,306 - -</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" s="5" t="n">
-        <v>-4.536907</v>
-      </c>
-      <c r="F129" s="5" t="n">
-        <v>-6.047206</v>
+        <v>2.785306</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6645,20 +6651,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>December 31, 2022 58,831,801 $ 37,200,411 $ 2,212,430 $ (992,917) $</t>
+          <t>Flow-through share premium (Note 8) - (455,934) - -</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" s="5" t="n">
-        <v>21.424561</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>-16.995363</v>
+        <v>-0.455934</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6674,17 +6682,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>of shares         Amount                       reserves              reserves                 Deficit                 Total</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Issuance of units for cash (Note 8) 29,166,123 5,875,730 138,331 -</t>
+          <t>Share issue costs (Note 8) - (95,745) - -</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" s="5" t="n">
-        <v>6.014061</v>
+        <v>-0.095745</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -6705,17 +6713,17 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Issuance of common shares for share issue</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Flow-through share premium (Note 8) - (175,627) - -</t>
+          <t>Issuance of common shares for share issue costs (Note 8) 267,907 70,353 - -</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" s="5" t="n">
-        <v>-0.175627</v>
+        <v>0.070353</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -6736,17 +6744,19 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
+          <t>Issuance of common shares on settlement</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Share issue costs - (299,159) 74,677 -</t>
+          <t>Issuance of common shares on settlement of restricted share units (Notes 8 and 9) 850,000 212,984 (212,984) -</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="n">
-        <v>-0.224482</v>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -6767,17 +6777,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>exploration and evaluation assets</t>
+          <t>Issuance of common shares on conversion</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>(Notes 5 and 8) 4,369,370 1,057,491 - -</t>
+          <t>Issuance of common shares on conversion of convertible debentures (Notes 7 and 8) 2,005,166 331,787 - -</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" s="5" t="n">
-        <v>1.057491</v>
+        <v>0.331787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -6803,12 +6813,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Issuance of common shares on exercise of options (Notes 8 and 9) 200 250 (114) -</t>
+          <t>Issuance of common shares on exercise of warrants (Note 8) 1,348,432 375,675 (11,123) -</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" s="5" t="n">
-        <v>0.000136</v>
+        <v>0.364552</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -6829,17 +6839,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>accounts payable and accrued liabilities</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>(Note 8) 405,405 94,139 - -</t>
+          <t>Debt unit warrants (Note 7) - - 128,304 -</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" s="5" t="n">
-        <v>0.094139</v>
+        <v>0.128304</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -6860,12 +6870,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of restricted share units (Notes 8 and 9) 150,000 65,895 (65,895) -</t>
+          <t>Options forfeited or expired (Note 9) - - (22,817) -</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -6874,10 +6884,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F137" s="5" t="n">
+        <v>0.022817</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -6893,12 +6901,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Options forfeited or expired (Note 9) - - (269,307) -</t>
+          <t>Warrants expired (Note 8) - 296,186 (297,757) -</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -6908,7 +6916,7 @@
         </is>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.269307</v>
+        <v>0.001571</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -6924,22 +6932,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Warrants expired (Note 8) - 358,649 (410,661) -</t>
+          <t>Share-based compensation (Note 9) - - 299,373 -</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" s="5" t="n">
-        <v>0.052012</v>
+      <c r="E139" s="5" t="n">
+        <v>0.299373</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -6955,17 +6963,17 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 9) - - 316,925 -</t>
+          <t>Foreign currency translation - - - (1,788,643)</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" s="5" t="n">
-        <v>0.316925</v>
+        <v>-1.788643</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -6986,22 +6994,24 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Foreign currency translation - - - 504,337</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E141" s="5" t="n">
-        <v>0.504337</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.047206</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>-6.047206</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7017,398 +7027,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Issuance of common shares on settlement of</t>
+          <t>Issuance of common shares on exercise of</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Loss for the year - - - -</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>December 31, 2024 107,869,395 $ 47,698,391 $ 1,879,382 $ (2,277,223) $</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" s="5" t="n">
-        <v>-4.536907</v>
+        <v>20.066781</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>-4.536907</v>
+        <v>-27.233769</v>
       </c>
       <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on settlement of</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>December 31, 2023 92,922,899 $ 44,177,779 $ 1,996,386 $ (488,580) $</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="n">
-        <v>24.474634</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>-21.210951</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Issuance of units for cash (Note 8) 10,474,991 2,785,306 - -</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" s="5" t="n">
-        <v>2.785306</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Flow-through share premium (Note 8) - (455,934) - -</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" s="5" t="n">
-        <v>-0.455934</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>of shares Amount reserves reserves Deficit Total</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Share issue costs (Note 8) - (95,745) - -</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" s="5" t="n">
-        <v>-0.095745</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Issuance of common shares for share issue</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Issuance of common shares for share issue costs (Note 8) 267,907 70,353 - -</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" s="5" t="n">
-        <v>0.070353</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on settlement</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on settlement of restricted share units (Notes 8 and 9) 850,000 212,984 (212,984) -</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on conversion</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on conversion of convertible debentures (Notes 7 and 8) 2,005,166 331,787 - -</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" s="5" t="n">
-        <v>0.331787</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on exercise of</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on exercise of warrants (Note 8) 1,348,432 375,675 (11,123) -</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" s="5" t="n">
-        <v>0.364552</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on exercise of</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Debt unit warrants (Note 7) - - 128,304 -</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" s="5" t="n">
-        <v>0.128304</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on exercise of</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Options forfeited or expired (Note 9) - - (22,817) -</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F152" s="5" t="n">
-        <v>0.022817</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on exercise of</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Warrants expired (Note 8) - 296,186 (297,757) -</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F153" s="5" t="n">
-        <v>0.001571</v>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Issuance of common shares on exercise of</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Share-based compensation (Note 9) - - 299,373 -</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" s="5" t="n">
-        <v>0.299373</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/KUYA.xlsx
+++ b/output/pdf_financials_xlsx/KUYA.xlsx
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.507806</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>-0.397841</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.684257</v>
       </c>
     </row>
     <row r="93">
@@ -3128,7 +3128,11 @@
           <t>Reserves (Notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3533,7 +3537,11 @@
           <t>Reserves (Notes 7, 8, and 9)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
         <v>1.507806</v>
       </c>

--- a/output/pdf_financials_xlsx/KUYA.xlsx
+++ b/output/pdf_financials_xlsx/KUYA.xlsx
@@ -620,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.036003</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.046986</v>
       </c>
     </row>
     <row r="13">
@@ -872,10 +872,10 @@
         <v>-4.536907</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.047206</v>
+        <v>-6.083209</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.584373</v>
+        <v>-3.631359</v>
       </c>
     </row>
     <row r="28">
@@ -904,10 +904,10 @@
         <v>-4.451235</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.045855</v>
+        <v>-6.081858</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.543101</v>
+        <v>-3.590087</v>
       </c>
     </row>
     <row r="30">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-4027.106688248106</v>
+        <v>-4051.088064264732</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.650187</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.7655650000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>9.339022999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.650187</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.7655650000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>9.339022999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.799645</v>
+        <v>0.149458</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.826383</v>
+        <v>0.060818</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>9.084403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">

--- a/output/pdf_financials_xlsx/KUYA.xlsx
+++ b/output/pdf_financials_xlsx/KUYA.xlsx
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.750546</v>
+        <v>0.850534</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.866157</v>
+        <v>0.96465</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.11457</v>
+        <v>1.220104</v>
       </c>
     </row>
     <row r="8">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.057136</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.062277</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.115266</v>
       </c>
     </row>
     <row r="68">
@@ -2229,13 +2229,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.059693</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.108765</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.071102</v>
       </c>
     </row>
     <row r="111">
@@ -3632,7 +3632,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>0.059693</v>
       </c>
@@ -4734,7 +4738,11 @@
           <t>Directors’ fees (Note 12)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -5834,7 +5842,11 @@
           <t>Directors’ fees (Note 11)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
         <v>0.09998799999999999</v>
       </c>
